--- a/Data/Home/LivingRoom.Door001.xlsx
+++ b/Data/Home/LivingRoom.Door001.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H326"/>
+  <dimension ref="A1:I365"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -469,6 +469,11 @@
           <t>actionSource</t>
         </is>
       </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>violationLabel</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -487,7 +492,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1709249189</v>
+        <v>1711846165</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -505,6 +510,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -523,7 +529,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1709253122</v>
+        <v>1711846207</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -541,6 +547,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -559,7 +566,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1709253585</v>
+        <v>1711846227</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -577,6 +584,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -595,7 +603,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1709253602</v>
+        <v>1711846285</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -613,6 +621,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -631,7 +640,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1709254690</v>
+        <v>1711847500</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -649,6 +658,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -667,7 +677,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1709254723</v>
+        <v>1711847556</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -685,6 +695,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -703,7 +714,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1709261531</v>
+        <v>1711859106</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -721,6 +732,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -739,7 +751,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1709261539</v>
+        <v>1711859114</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -757,6 +769,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -775,7 +788,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1709261547</v>
+        <v>1711862388</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -793,6 +806,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -811,7 +825,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1709262566</v>
+        <v>1711862398</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -829,6 +843,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -847,7 +862,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1709262578</v>
+        <v>1711868475</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -865,6 +880,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -883,7 +899,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>1709265322</v>
+        <v>1711868484</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -901,6 +917,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -919,7 +936,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1709266294</v>
+        <v>1711931034</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -937,6 +954,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -955,7 +973,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>1709266320</v>
+        <v>1711931099</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -973,6 +991,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -991,7 +1010,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>1709270038</v>
+        <v>1711932709</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -1009,6 +1028,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1027,7 +1047,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>1709270045</v>
+        <v>1711932772</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -1045,6 +1065,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1063,7 +1084,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>1709271572</v>
+        <v>1711945228</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -1081,6 +1102,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1099,7 +1121,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>1709271588</v>
+        <v>1711945240</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -1117,6 +1139,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1135,7 +1158,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>1709271608</v>
+        <v>1711956422</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -1153,6 +1176,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1171,7 +1195,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>1709272679</v>
+        <v>1711956434</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -1189,6 +1213,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1207,7 +1232,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>1709273120</v>
+        <v>1711961812</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -1225,6 +1250,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1243,7 +1269,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>1709246812</v>
+        <v>1711961821</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -1261,6 +1287,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1279,7 +1306,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>1709247508</v>
+        <v>1712019450</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -1297,6 +1324,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1315,7 +1343,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>1709247525</v>
+        <v>1712019474</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -1333,6 +1361,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1351,7 +1380,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>1709247726</v>
+        <v>1712019733</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -1369,6 +1398,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1387,7 +1417,7 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>1709247773</v>
+        <v>1712019791</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -1405,6 +1435,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1423,7 +1454,7 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>1709256939</v>
+        <v>1712020095</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -1441,6 +1472,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1459,7 +1491,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>1709256947</v>
+        <v>1712020162</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -1477,6 +1509,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1495,7 +1528,7 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>1709259673</v>
+        <v>1712036816</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -1513,6 +1546,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1531,7 +1565,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>1709259678</v>
+        <v>1712036824</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -1549,6 +1583,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1567,7 +1602,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>1709260163</v>
+        <v>1712038353</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
@@ -1585,6 +1620,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1603,7 +1639,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>1709268850</v>
+        <v>1712038361</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
@@ -1621,6 +1657,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1639,7 +1676,7 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>1709268861</v>
+        <v>1712042090</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
@@ -1657,6 +1694,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1675,7 +1713,7 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>1709332712</v>
+        <v>1712042096</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
@@ -1693,6 +1731,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1711,7 +1750,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>1709333576</v>
+        <v>1712104666</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
@@ -1729,6 +1768,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1747,7 +1787,7 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>1709333613</v>
+        <v>1712104733</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
@@ -1765,6 +1805,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1783,7 +1824,7 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>1709333975</v>
+        <v>1712106258</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
@@ -1801,6 +1842,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1819,7 +1861,7 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>1709334006</v>
+        <v>1712106313</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
@@ -1837,6 +1879,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1855,7 +1898,7 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>1709342728</v>
+        <v>1712106391</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
@@ -1873,6 +1916,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1891,7 +1935,7 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>1709342738</v>
+        <v>1712106411</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
@@ -1909,6 +1953,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1927,7 +1972,7 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>1709345205</v>
+        <v>1712115919</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
@@ -1945,6 +1990,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1963,7 +2009,7 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>1709345893</v>
+        <v>1712115923</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
@@ -1981,6 +2027,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1999,7 +2046,7 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>1709348457</v>
+        <v>1712121043</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
@@ -2017,6 +2064,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2035,7 +2083,7 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>1709352585</v>
+        <v>1712121079</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
@@ -2053,6 +2101,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2071,7 +2120,7 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>1709352601</v>
+        <v>1712122996</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
@@ -2089,6 +2138,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2107,7 +2157,7 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>1709419298</v>
+        <v>1712123007</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
@@ -2125,6 +2175,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2143,7 +2194,7 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>1709420270</v>
+        <v>1712127740</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
@@ -2161,6 +2212,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -2179,7 +2231,7 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>1709420301</v>
+        <v>1712127752</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
@@ -2197,6 +2249,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2215,7 +2268,7 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>1709420591</v>
+        <v>1712128169</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
@@ -2233,6 +2286,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2251,7 +2305,7 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>1709420636</v>
+        <v>1712128183</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
@@ -2269,6 +2323,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2287,7 +2342,7 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>1709428488</v>
+        <v>1712191086</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
@@ -2305,6 +2360,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2323,7 +2379,7 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>1709428507</v>
+        <v>1712191140</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
@@ -2341,6 +2397,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2359,7 +2416,7 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>1709432454</v>
+        <v>1712192709</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
@@ -2377,6 +2434,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2395,7 +2453,7 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>1709432485</v>
+        <v>1712192745</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
@@ -2413,6 +2471,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2431,7 +2490,7 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>1709438378</v>
+        <v>1712193066</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
@@ -2449,6 +2508,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2467,7 +2527,7 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>1709438402</v>
+        <v>1712193119</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
@@ -2485,6 +2545,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2503,7 +2564,7 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>1709439254</v>
+        <v>1712201305</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
@@ -2521,6 +2582,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -2539,7 +2601,7 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>1709439262</v>
+        <v>1712201313</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
@@ -2557,6 +2619,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -2575,7 +2638,7 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>1709439280</v>
+        <v>1712201333</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
@@ -2593,6 +2656,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -2611,7 +2675,7 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>1709440404</v>
+        <v>1712201367</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
@@ -2629,6 +2693,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -2647,7 +2712,7 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>1709442215</v>
+        <v>1712202362</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
@@ -2665,6 +2730,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -2683,7 +2749,7 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>1709504956</v>
+        <v>1712202370</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
@@ -2701,6 +2767,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -2719,7 +2786,7 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>1709506175</v>
+        <v>1712202810</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
@@ -2737,6 +2804,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -2755,7 +2823,7 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>1709506214</v>
+        <v>1712202817</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
@@ -2773,6 +2841,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -2791,7 +2860,7 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>1709506245</v>
+        <v>1712205970</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
@@ -2809,6 +2878,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -2827,7 +2897,7 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>1709506262</v>
+        <v>1712205978</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
@@ -2845,6 +2915,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -2863,7 +2934,7 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>1709514381</v>
+        <v>1712208030</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
@@ -2881,6 +2952,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -2899,7 +2971,7 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>1709514396</v>
+        <v>1712208103</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
@@ -2917,6 +2989,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -2935,7 +3008,7 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>1709515530</v>
+        <v>1712209511</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
@@ -2953,6 +3026,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -2971,7 +3045,7 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>1709515541</v>
+        <v>1712209521</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
@@ -2989,6 +3063,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -3007,7 +3082,7 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>1709515564</v>
+        <v>1712276896</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
@@ -3025,6 +3100,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -3043,7 +3119,7 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>1709519820</v>
+        <v>1712276948</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
@@ -3061,6 +3137,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -3079,7 +3156,7 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>1709523855</v>
+        <v>1712279106</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
@@ -3097,6 +3174,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -3115,7 +3193,7 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>1709525244</v>
+        <v>1712279165</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
@@ -3133,6 +3211,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -3151,7 +3230,7 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>1709528059</v>
+        <v>1712279203</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
@@ -3169,6 +3248,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -3187,7 +3267,7 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>1709528073</v>
+        <v>1712279240</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
@@ -3205,6 +3285,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -3223,7 +3304,7 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>1709528094</v>
+        <v>1712288273</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
@@ -3241,6 +3322,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -3259,7 +3341,7 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>1709591904</v>
+        <v>1712288280</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
@@ -3277,6 +3359,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -3295,7 +3378,7 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>1709593168</v>
+        <v>1712294391</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
@@ -3313,6 +3396,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -3331,7 +3415,7 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>1709593196</v>
+        <v>1712294467</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
@@ -3349,6 +3433,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -3367,7 +3452,7 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>1709601883</v>
+        <v>1712295391</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
@@ -3385,6 +3470,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -3403,7 +3489,7 @@
         </is>
       </c>
       <c r="D83" t="n">
-        <v>1709601897</v>
+        <v>1712295397</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
@@ -3421,6 +3507,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -3439,7 +3526,7 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>1709604082</v>
+        <v>1712297070</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
@@ -3457,6 +3544,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -3475,7 +3563,7 @@
         </is>
       </c>
       <c r="D85" t="n">
-        <v>1709604089</v>
+        <v>1712297082</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
@@ -3493,6 +3581,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -3511,7 +3600,7 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>1709606149</v>
+        <v>1712306068</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
@@ -3529,6 +3618,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -3547,7 +3637,7 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>1709606179</v>
+        <v>1712306083</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
@@ -3565,6 +3655,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -3583,7 +3674,7 @@
         </is>
       </c>
       <c r="D88" t="n">
-        <v>1709608061</v>
+        <v>1712379707</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
@@ -3601,6 +3692,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -3619,7 +3711,7 @@
         </is>
       </c>
       <c r="D89" t="n">
-        <v>1709608929</v>
+        <v>1712379754</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
@@ -3637,6 +3729,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -3655,7 +3748,7 @@
         </is>
       </c>
       <c r="D90" t="n">
-        <v>1709608947</v>
+        <v>1712388755</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
@@ -3673,6 +3766,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -3691,7 +3785,7 @@
         </is>
       </c>
       <c r="D91" t="n">
-        <v>1709615728</v>
+        <v>1712388764</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
@@ -3709,6 +3803,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -3727,7 +3822,7 @@
         </is>
       </c>
       <c r="D92" t="n">
-        <v>1709620058</v>
+        <v>1712473219</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
@@ -3745,6 +3840,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -3763,7 +3859,7 @@
         </is>
       </c>
       <c r="D93" t="n">
-        <v>1709776944</v>
+        <v>1712473283</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
@@ -3781,6 +3877,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -3799,7 +3896,7 @@
         </is>
       </c>
       <c r="D94" t="n">
-        <v>1709783754</v>
+        <v>1712482495</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
@@ -3817,6 +3914,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -3835,7 +3933,7 @@
         </is>
       </c>
       <c r="D95" t="n">
-        <v>1709783771</v>
+        <v>1712482504</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
@@ -3853,6 +3951,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -3871,7 +3970,7 @@
         </is>
       </c>
       <c r="D96" t="n">
-        <v>1709785678</v>
+        <v>1712536617</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
@@ -3889,6 +3988,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -3907,7 +4007,7 @@
         </is>
       </c>
       <c r="D97" t="n">
-        <v>1709851853</v>
+        <v>1712536667</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
@@ -3925,6 +4025,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -3943,7 +4044,7 @@
         </is>
       </c>
       <c r="D98" t="n">
-        <v>1709851980</v>
+        <v>1712537822</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
@@ -3961,6 +4062,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -3979,7 +4081,7 @@
         </is>
       </c>
       <c r="D99" t="n">
-        <v>1709852839</v>
+        <v>1712537848</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
@@ -3997,6 +4099,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -4015,7 +4118,7 @@
         </is>
       </c>
       <c r="D100" t="n">
-        <v>1709852949</v>
+        <v>1712538381</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
@@ -4033,6 +4136,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -4051,7 +4155,7 @@
         </is>
       </c>
       <c r="D101" t="n">
-        <v>1709852998</v>
+        <v>1712538425</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
@@ -4069,6 +4173,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -4087,7 +4192,7 @@
         </is>
       </c>
       <c r="D102" t="n">
-        <v>1709859832</v>
+        <v>1712548871</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
@@ -4105,6 +4210,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -4123,7 +4229,7 @@
         </is>
       </c>
       <c r="D103" t="n">
-        <v>1709859850</v>
+        <v>1712548877</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
@@ -4141,6 +4247,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -4159,7 +4266,7 @@
         </is>
       </c>
       <c r="D104" t="n">
-        <v>1709859861</v>
+        <v>1712551054</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
@@ -4177,6 +4284,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -4195,7 +4303,7 @@
         </is>
       </c>
       <c r="D105" t="n">
-        <v>1709863329</v>
+        <v>1712551059</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
@@ -4213,6 +4321,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -4231,7 +4340,7 @@
         </is>
       </c>
       <c r="D106" t="n">
-        <v>1709866105</v>
+        <v>1712555170</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
@@ -4249,6 +4358,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -4267,7 +4377,7 @@
         </is>
       </c>
       <c r="D107" t="n">
-        <v>1709866127</v>
+        <v>1712555179</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
@@ -4285,6 +4395,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -4303,7 +4414,7 @@
         </is>
       </c>
       <c r="D108" t="n">
-        <v>1709866133</v>
+        <v>1712556733</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
@@ -4321,6 +4432,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -4339,7 +4451,7 @@
         </is>
       </c>
       <c r="D109" t="n">
-        <v>1709866149</v>
+        <v>1712556786</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
@@ -4357,6 +4469,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -4375,7 +4488,7 @@
         </is>
       </c>
       <c r="D110" t="n">
-        <v>1709866155</v>
+        <v>1712559720</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
@@ -4393,6 +4506,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -4411,7 +4525,7 @@
         </is>
       </c>
       <c r="D111" t="n">
-        <v>1709869499</v>
+        <v>1712559727</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
@@ -4429,6 +4543,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -4447,7 +4562,7 @@
         </is>
       </c>
       <c r="D112" t="n">
-        <v>1709869590</v>
+        <v>1712623904</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
@@ -4465,6 +4580,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -4483,7 +4599,7 @@
         </is>
       </c>
       <c r="D113" t="n">
-        <v>1709938838</v>
+        <v>1712623973</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
@@ -4501,6 +4617,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -4519,7 +4636,7 @@
         </is>
       </c>
       <c r="D114" t="n">
-        <v>1709938864</v>
+        <v>1712624401</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
@@ -4537,6 +4654,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -4555,7 +4673,7 @@
         </is>
       </c>
       <c r="D115" t="n">
-        <v>1709938899</v>
+        <v>1712624443</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
@@ -4573,6 +4691,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -4591,7 +4710,7 @@
         </is>
       </c>
       <c r="D116" t="n">
-        <v>1709940299</v>
+        <v>1712625004</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
@@ -4609,6 +4728,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -4627,7 +4747,7 @@
         </is>
       </c>
       <c r="D117" t="n">
-        <v>1709940324</v>
+        <v>1712625061</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
@@ -4645,6 +4765,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -4663,7 +4784,7 @@
         </is>
       </c>
       <c r="D118" t="n">
-        <v>1709950214</v>
+        <v>1712634909</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
@@ -4681,6 +4802,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -4699,7 +4821,7 @@
         </is>
       </c>
       <c r="D119" t="n">
-        <v>1709950224</v>
+        <v>1712634916</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
@@ -4717,6 +4839,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -4735,7 +4858,7 @@
         </is>
       </c>
       <c r="D120" t="n">
-        <v>1709954347</v>
+        <v>1712636562</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
@@ -4753,6 +4876,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -4771,7 +4895,7 @@
         </is>
       </c>
       <c r="D121" t="n">
-        <v>1709958998</v>
+        <v>1712636571</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
@@ -4789,6 +4913,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -4807,7 +4932,7 @@
         </is>
       </c>
       <c r="D122" t="n">
-        <v>1709959051</v>
+        <v>1712639623</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
@@ -4825,6 +4950,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -4843,7 +4969,7 @@
         </is>
       </c>
       <c r="D123" t="n">
-        <v>1709959065</v>
+        <v>1712639634</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
@@ -4861,6 +4987,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -4879,7 +5006,7 @@
         </is>
       </c>
       <c r="D124" t="n">
-        <v>1709959084</v>
+        <v>1712640092</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
@@ -4897,6 +5024,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -4915,7 +5043,7 @@
         </is>
       </c>
       <c r="D125" t="n">
-        <v>1710024753</v>
+        <v>1712640129</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
@@ -4933,6 +5061,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -4951,7 +5080,7 @@
         </is>
       </c>
       <c r="D126" t="n">
-        <v>1710026417</v>
+        <v>1712644358</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
@@ -4969,6 +5098,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -4987,7 +5117,7 @@
         </is>
       </c>
       <c r="D127" t="n">
-        <v>1710026459</v>
+        <v>1712644367</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
@@ -5005,6 +5135,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -5023,7 +5154,7 @@
         </is>
       </c>
       <c r="D128" t="n">
-        <v>1710026565</v>
+        <v>1712709100</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
@@ -5041,6 +5172,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -5059,7 +5191,7 @@
         </is>
       </c>
       <c r="D129" t="n">
-        <v>1710026594</v>
+        <v>1712709154</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
@@ -5077,6 +5209,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -5095,7 +5228,7 @@
         </is>
       </c>
       <c r="D130" t="n">
-        <v>1710032366</v>
+        <v>1712709622</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
@@ -5113,6 +5246,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -5131,7 +5265,7 @@
         </is>
       </c>
       <c r="D131" t="n">
-        <v>1710032379</v>
+        <v>1712709656</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
@@ -5149,6 +5283,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -5167,7 +5302,7 @@
         </is>
       </c>
       <c r="D132" t="n">
-        <v>1710032385</v>
+        <v>1712711298</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
@@ -5185,6 +5320,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -5203,7 +5339,7 @@
         </is>
       </c>
       <c r="D133" t="n">
-        <v>1710033979</v>
+        <v>1712711323</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
@@ -5221,6 +5357,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -5239,7 +5376,7 @@
         </is>
       </c>
       <c r="D134" t="n">
-        <v>1710034863</v>
+        <v>1712719210</v>
       </c>
       <c r="E134" t="inlineStr">
         <is>
@@ -5257,6 +5394,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -5275,7 +5413,7 @@
         </is>
       </c>
       <c r="D135" t="n">
-        <v>1710034872</v>
+        <v>1712719220</v>
       </c>
       <c r="E135" t="inlineStr">
         <is>
@@ -5293,6 +5431,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -5311,7 +5450,7 @@
         </is>
       </c>
       <c r="D136" t="n">
-        <v>1710034882</v>
+        <v>1712724445</v>
       </c>
       <c r="E136" t="inlineStr">
         <is>
@@ -5329,6 +5468,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -5347,7 +5487,7 @@
         </is>
       </c>
       <c r="D137" t="n">
-        <v>1710037127</v>
+        <v>1712724493</v>
       </c>
       <c r="E137" t="inlineStr">
         <is>
@@ -5365,6 +5505,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -5383,7 +5524,7 @@
         </is>
       </c>
       <c r="D138" t="n">
-        <v>1710037749</v>
+        <v>1712725835</v>
       </c>
       <c r="E138" t="inlineStr">
         <is>
@@ -5401,6 +5542,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -5419,7 +5561,7 @@
         </is>
       </c>
       <c r="D139" t="n">
-        <v>1710037774</v>
+        <v>1712725844</v>
       </c>
       <c r="E139" t="inlineStr">
         <is>
@@ -5437,6 +5579,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -5455,7 +5598,7 @@
         </is>
       </c>
       <c r="D140" t="n">
-        <v>1710038637</v>
+        <v>1712726891</v>
       </c>
       <c r="E140" t="inlineStr">
         <is>
@@ -5473,6 +5616,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -5491,7 +5635,7 @@
         </is>
       </c>
       <c r="D141" t="n">
-        <v>1710038657</v>
+        <v>1712726904</v>
       </c>
       <c r="E141" t="inlineStr">
         <is>
@@ -5509,6 +5653,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -5527,7 +5672,7 @@
         </is>
       </c>
       <c r="D142" t="n">
-        <v>1710041388</v>
+        <v>1712740000</v>
       </c>
       <c r="E142" t="inlineStr">
         <is>
@@ -5545,6 +5690,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -5563,7 +5709,7 @@
         </is>
       </c>
       <c r="D143" t="n">
-        <v>1710041410</v>
+        <v>1712740010</v>
       </c>
       <c r="E143" t="inlineStr">
         <is>
@@ -5581,6 +5727,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -5599,7 +5746,7 @@
         </is>
       </c>
       <c r="D144" t="n">
-        <v>1710041436</v>
+        <v>1712794915</v>
       </c>
       <c r="E144" t="inlineStr">
         <is>
@@ -5617,6 +5764,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -5635,7 +5783,7 @@
         </is>
       </c>
       <c r="D145" t="n">
-        <v>1710046389</v>
+        <v>1712794964</v>
       </c>
       <c r="E145" t="inlineStr">
         <is>
@@ -5653,6 +5801,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -5671,7 +5820,7 @@
         </is>
       </c>
       <c r="D146" t="n">
-        <v>1710047947</v>
+        <v>1712796165</v>
       </c>
       <c r="E146" t="inlineStr">
         <is>
@@ -5689,6 +5838,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -5707,7 +5857,7 @@
         </is>
       </c>
       <c r="D147" t="n">
-        <v>1710110030</v>
+        <v>1712796226</v>
       </c>
       <c r="E147" t="inlineStr">
         <is>
@@ -5725,6 +5875,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -5743,7 +5894,7 @@
         </is>
       </c>
       <c r="D148" t="n">
-        <v>1710111185</v>
+        <v>1712796256</v>
       </c>
       <c r="E148" t="inlineStr">
         <is>
@@ -5761,6 +5912,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -5779,7 +5931,7 @@
         </is>
       </c>
       <c r="D149" t="n">
-        <v>1710111238</v>
+        <v>1712796270</v>
       </c>
       <c r="E149" t="inlineStr">
         <is>
@@ -5797,6 +5949,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -5815,7 +5968,7 @@
         </is>
       </c>
       <c r="D150" t="n">
-        <v>1710112118</v>
+        <v>1712804428</v>
       </c>
       <c r="E150" t="inlineStr">
         <is>
@@ -5833,6 +5986,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -5851,7 +6005,7 @@
         </is>
       </c>
       <c r="D151" t="n">
-        <v>1710112185</v>
+        <v>1712804438</v>
       </c>
       <c r="E151" t="inlineStr">
         <is>
@@ -5869,6 +6023,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -5887,7 +6042,7 @@
         </is>
       </c>
       <c r="D152" t="n">
-        <v>1710121545</v>
+        <v>1712809570</v>
       </c>
       <c r="E152" t="inlineStr">
         <is>
@@ -5905,6 +6060,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -5923,7 +6079,7 @@
         </is>
       </c>
       <c r="D153" t="n">
-        <v>1710121555</v>
+        <v>1712809627</v>
       </c>
       <c r="E153" t="inlineStr">
         <is>
@@ -5941,6 +6097,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -5959,7 +6116,7 @@
         </is>
       </c>
       <c r="D154" t="n">
-        <v>1710121563</v>
+        <v>1712811389</v>
       </c>
       <c r="E154" t="inlineStr">
         <is>
@@ -5977,6 +6134,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -5995,7 +6153,7 @@
         </is>
       </c>
       <c r="D155" t="n">
-        <v>1710125275</v>
+        <v>1712811399</v>
       </c>
       <c r="E155" t="inlineStr">
         <is>
@@ -6013,6 +6171,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -6031,7 +6190,7 @@
         </is>
       </c>
       <c r="D156" t="n">
-        <v>1710130101</v>
+        <v>1712811956</v>
       </c>
       <c r="E156" t="inlineStr">
         <is>
@@ -6049,6 +6208,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -6067,7 +6227,7 @@
         </is>
       </c>
       <c r="D157" t="n">
-        <v>1710132646</v>
+        <v>1712811965</v>
       </c>
       <c r="E157" t="inlineStr">
         <is>
@@ -6085,6 +6245,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -6103,7 +6264,7 @@
         </is>
       </c>
       <c r="D158" t="n">
-        <v>1710134970</v>
+        <v>1712813810</v>
       </c>
       <c r="E158" t="inlineStr">
         <is>
@@ -6121,6 +6282,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -6139,7 +6301,7 @@
         </is>
       </c>
       <c r="D159" t="n">
-        <v>1710199457</v>
+        <v>1712813822</v>
       </c>
       <c r="E159" t="inlineStr">
         <is>
@@ -6157,6 +6319,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -6175,7 +6338,7 @@
         </is>
       </c>
       <c r="D160" t="n">
-        <v>1710200497</v>
+        <v>1712881109</v>
       </c>
       <c r="E160" t="inlineStr">
         <is>
@@ -6193,6 +6356,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -6211,7 +6375,7 @@
         </is>
       </c>
       <c r="D161" t="n">
-        <v>1710200537</v>
+        <v>1712881178</v>
       </c>
       <c r="E161" t="inlineStr">
         <is>
@@ -6229,6 +6393,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -6247,7 +6412,7 @@
         </is>
       </c>
       <c r="D162" t="n">
-        <v>1710200636</v>
+        <v>1712882846</v>
       </c>
       <c r="E162" t="inlineStr">
         <is>
@@ -6265,6 +6430,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -6283,7 +6449,7 @@
         </is>
       </c>
       <c r="D163" t="n">
-        <v>1710200691</v>
+        <v>1712882912</v>
       </c>
       <c r="E163" t="inlineStr">
         <is>
@@ -6301,6 +6467,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -6319,7 +6486,7 @@
         </is>
       </c>
       <c r="D164" t="n">
-        <v>1710210152</v>
+        <v>1712882969</v>
       </c>
       <c r="E164" t="inlineStr">
         <is>
@@ -6337,6 +6504,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -6355,7 +6523,7 @@
         </is>
       </c>
       <c r="D165" t="n">
-        <v>1710210165</v>
+        <v>1712883007</v>
       </c>
       <c r="E165" t="inlineStr">
         <is>
@@ -6373,6 +6541,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -6391,7 +6560,7 @@
         </is>
       </c>
       <c r="D166" t="n">
-        <v>1710212233</v>
+        <v>1712891143</v>
       </c>
       <c r="E166" t="inlineStr">
         <is>
@@ -6409,6 +6578,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -6427,7 +6597,7 @@
         </is>
       </c>
       <c r="D167" t="n">
-        <v>1710212242</v>
+        <v>1712891150</v>
       </c>
       <c r="E167" t="inlineStr">
         <is>
@@ -6445,6 +6615,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -6463,7 +6634,7 @@
         </is>
       </c>
       <c r="D168" t="n">
-        <v>1710213892</v>
+        <v>1712891163</v>
       </c>
       <c r="E168" t="inlineStr">
         <is>
@@ -6481,6 +6652,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -6499,7 +6671,7 @@
         </is>
       </c>
       <c r="D169" t="n">
-        <v>1710222790</v>
+        <v>1712891204</v>
       </c>
       <c r="E169" t="inlineStr">
         <is>
@@ -6517,6 +6689,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -6535,7 +6708,7 @@
         </is>
       </c>
       <c r="D170" t="n">
-        <v>1710222809</v>
+        <v>1712894162</v>
       </c>
       <c r="E170" t="inlineStr">
         <is>
@@ -6553,6 +6726,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -6571,7 +6745,7 @@
         </is>
       </c>
       <c r="D171" t="n">
-        <v>1710458732</v>
+        <v>1712894170</v>
       </c>
       <c r="E171" t="inlineStr">
         <is>
@@ -6589,6 +6763,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -6607,7 +6782,7 @@
         </is>
       </c>
       <c r="D172" t="n">
-        <v>1710459458</v>
+        <v>1712899871</v>
       </c>
       <c r="E172" t="inlineStr">
         <is>
@@ -6625,6 +6800,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -6643,7 +6819,7 @@
         </is>
       </c>
       <c r="D173" t="n">
-        <v>1710459490</v>
+        <v>1712899880</v>
       </c>
       <c r="E173" t="inlineStr">
         <is>
@@ -6661,6 +6837,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -6679,7 +6856,7 @@
         </is>
       </c>
       <c r="D174" t="n">
-        <v>1710459872</v>
+        <v>1712900437</v>
       </c>
       <c r="E174" t="inlineStr">
         <is>
@@ -6697,6 +6874,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -6715,7 +6893,7 @@
         </is>
       </c>
       <c r="D175" t="n">
-        <v>1710459910</v>
+        <v>1712900467</v>
       </c>
       <c r="E175" t="inlineStr">
         <is>
@@ -6733,6 +6911,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -6751,7 +6930,7 @@
         </is>
       </c>
       <c r="D176" t="n">
-        <v>1710473087</v>
+        <v>1712902560</v>
       </c>
       <c r="E176" t="inlineStr">
         <is>
@@ -6769,6 +6948,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -6787,7 +6967,7 @@
         </is>
       </c>
       <c r="D177" t="n">
-        <v>1710473095</v>
+        <v>1712902569</v>
       </c>
       <c r="E177" t="inlineStr">
         <is>
@@ -6805,6 +6985,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -6823,7 +7004,7 @@
         </is>
       </c>
       <c r="D178" t="n">
-        <v>1710476569</v>
+        <v>1712905197</v>
       </c>
       <c r="E178" t="inlineStr">
         <is>
@@ -6841,6 +7022,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -6859,7 +7041,7 @@
         </is>
       </c>
       <c r="D179" t="n">
-        <v>1710477631</v>
+        <v>1712905210</v>
       </c>
       <c r="E179" t="inlineStr">
         <is>
@@ -6877,6 +7059,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -6895,7 +7078,7 @@
         </is>
       </c>
       <c r="D180" t="n">
-        <v>1710477651</v>
+        <v>1712982370</v>
       </c>
       <c r="E180" t="inlineStr">
         <is>
@@ -6913,6 +7096,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -6931,7 +7115,7 @@
         </is>
       </c>
       <c r="D181" t="n">
-        <v>1710481893</v>
+        <v>1712982412</v>
       </c>
       <c r="E181" t="inlineStr">
         <is>
@@ -6949,6 +7133,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -6967,7 +7152,7 @@
         </is>
       </c>
       <c r="D182" t="n">
-        <v>1710481899</v>
+        <v>1712991951</v>
       </c>
       <c r="E182" t="inlineStr">
         <is>
@@ -6985,6 +7170,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -7003,7 +7189,7 @@
         </is>
       </c>
       <c r="D183" t="n">
-        <v>1710542846</v>
+        <v>1712991960</v>
       </c>
       <c r="E183" t="inlineStr">
         <is>
@@ -7021,6 +7207,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -7039,7 +7226,7 @@
         </is>
       </c>
       <c r="D184" t="n">
-        <v>1710543352</v>
+        <v>1713070249</v>
       </c>
       <c r="E184" t="inlineStr">
         <is>
@@ -7057,6 +7244,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -7075,7 +7263,7 @@
         </is>
       </c>
       <c r="D185" t="n">
-        <v>1710543387</v>
+        <v>1713070294</v>
       </c>
       <c r="E185" t="inlineStr">
         <is>
@@ -7093,6 +7281,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -7111,7 +7300,7 @@
         </is>
       </c>
       <c r="D186" t="n">
-        <v>1710543915</v>
+        <v>1713073595</v>
       </c>
       <c r="E186" t="inlineStr">
         <is>
@@ -7129,6 +7318,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -7147,7 +7337,7 @@
         </is>
       </c>
       <c r="D187" t="n">
-        <v>1710543933</v>
+        <v>1713073627</v>
       </c>
       <c r="E187" t="inlineStr">
         <is>
@@ -7165,6 +7355,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -7183,7 +7374,7 @@
         </is>
       </c>
       <c r="D188" t="n">
-        <v>1710551355</v>
+        <v>1713079574</v>
       </c>
       <c r="E188" t="inlineStr">
         <is>
@@ -7201,6 +7392,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -7219,7 +7411,7 @@
         </is>
       </c>
       <c r="D189" t="n">
-        <v>1710551363</v>
+        <v>1713079587</v>
       </c>
       <c r="E189" t="inlineStr">
         <is>
@@ -7237,6 +7429,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -7255,7 +7448,7 @@
         </is>
       </c>
       <c r="D190" t="n">
-        <v>1710551747</v>
+        <v>1713082941</v>
       </c>
       <c r="E190" t="inlineStr">
         <is>
@@ -7273,6 +7466,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -7291,7 +7485,7 @@
         </is>
       </c>
       <c r="D191" t="n">
-        <v>1710551767</v>
+        <v>1713082949</v>
       </c>
       <c r="E191" t="inlineStr">
         <is>
@@ -7309,6 +7503,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -7327,7 +7522,7 @@
         </is>
       </c>
       <c r="D192" t="n">
-        <v>1710551773</v>
+        <v>1713141036</v>
       </c>
       <c r="E192" t="inlineStr">
         <is>
@@ -7345,6 +7540,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -7363,7 +7559,7 @@
         </is>
       </c>
       <c r="D193" t="n">
-        <v>1710555082</v>
+        <v>1713141086</v>
       </c>
       <c r="E193" t="inlineStr">
         <is>
@@ -7381,6 +7577,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -7399,7 +7596,7 @@
         </is>
       </c>
       <c r="D194" t="n">
-        <v>1710555145</v>
+        <v>1713141179</v>
       </c>
       <c r="E194" t="inlineStr">
         <is>
@@ -7417,6 +7614,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -7435,7 +7633,7 @@
         </is>
       </c>
       <c r="D195" t="n">
-        <v>1710555175</v>
+        <v>1713141251</v>
       </c>
       <c r="E195" t="inlineStr">
         <is>
@@ -7453,6 +7651,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I195" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -7471,7 +7670,7 @@
         </is>
       </c>
       <c r="D196" t="n">
-        <v>1710555924</v>
+        <v>1713143297</v>
       </c>
       <c r="E196" t="inlineStr">
         <is>
@@ -7489,6 +7688,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I196" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -7507,7 +7707,7 @@
         </is>
       </c>
       <c r="D197" t="n">
-        <v>1710555936</v>
+        <v>1713143334</v>
       </c>
       <c r="E197" t="inlineStr">
         <is>
@@ -7525,6 +7725,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I197" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -7543,7 +7744,7 @@
         </is>
       </c>
       <c r="D198" t="n">
-        <v>1710560090</v>
+        <v>1713151417</v>
       </c>
       <c r="E198" t="inlineStr">
         <is>
@@ -7561,6 +7762,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -7579,7 +7781,7 @@
         </is>
       </c>
       <c r="D199" t="n">
-        <v>1710560538</v>
+        <v>1713151426</v>
       </c>
       <c r="E199" t="inlineStr">
         <is>
@@ -7597,6 +7799,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I199" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -7615,7 +7818,7 @@
         </is>
       </c>
       <c r="D200" t="n">
-        <v>1710560548</v>
+        <v>1713153453</v>
       </c>
       <c r="E200" t="inlineStr">
         <is>
@@ -7633,6 +7836,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I200" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -7651,7 +7855,7 @@
         </is>
       </c>
       <c r="D201" t="n">
-        <v>1710560890</v>
+        <v>1713153458</v>
       </c>
       <c r="E201" t="inlineStr">
         <is>
@@ -7669,6 +7873,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I201" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -7687,7 +7892,7 @@
         </is>
       </c>
       <c r="D202" t="n">
-        <v>1710563955</v>
+        <v>1713156702</v>
       </c>
       <c r="E202" t="inlineStr">
         <is>
@@ -7705,6 +7910,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I202" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -7723,7 +7929,7 @@
         </is>
       </c>
       <c r="D203" t="n">
-        <v>1710629209</v>
+        <v>1713156745</v>
       </c>
       <c r="E203" t="inlineStr">
         <is>
@@ -7741,6 +7947,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I203" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -7759,7 +7966,7 @@
         </is>
       </c>
       <c r="D204" t="n">
-        <v>1710630295</v>
+        <v>1713158923</v>
       </c>
       <c r="E204" t="inlineStr">
         <is>
@@ -7777,6 +7984,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I204" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -7795,7 +8003,7 @@
         </is>
       </c>
       <c r="D205" t="n">
-        <v>1710630330</v>
+        <v>1713158979</v>
       </c>
       <c r="E205" t="inlineStr">
         <is>
@@ -7813,6 +8021,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I205" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -7831,7 +8040,7 @@
         </is>
       </c>
       <c r="D206" t="n">
-        <v>1710630457</v>
+        <v>1713160201</v>
       </c>
       <c r="E206" t="inlineStr">
         <is>
@@ -7849,6 +8058,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I206" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -7867,7 +8077,7 @@
         </is>
       </c>
       <c r="D207" t="n">
-        <v>1710630507</v>
+        <v>1713160215</v>
       </c>
       <c r="E207" t="inlineStr">
         <is>
@@ -7885,6 +8095,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I207" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -7903,7 +8114,7 @@
         </is>
       </c>
       <c r="D208" t="n">
-        <v>1710642391</v>
+        <v>1713167214</v>
       </c>
       <c r="E208" t="inlineStr">
         <is>
@@ -7921,6 +8132,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I208" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -7939,7 +8151,7 @@
         </is>
       </c>
       <c r="D209" t="n">
-        <v>1710642426</v>
+        <v>1713167224</v>
       </c>
       <c r="E209" t="inlineStr">
         <is>
@@ -7957,6 +8169,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I209" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -7975,7 +8188,7 @@
         </is>
       </c>
       <c r="D210" t="n">
-        <v>1710643501</v>
+        <v>1713168799</v>
       </c>
       <c r="E210" t="inlineStr">
         <is>
@@ -7993,6 +8206,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I210" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -8011,7 +8225,7 @@
         </is>
       </c>
       <c r="D211" t="n">
-        <v>1710643513</v>
+        <v>1713168806</v>
       </c>
       <c r="E211" t="inlineStr">
         <is>
@@ -8029,6 +8243,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I211" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -8047,7 +8262,7 @@
         </is>
       </c>
       <c r="D212" t="n">
-        <v>1710643524</v>
+        <v>1713227603</v>
       </c>
       <c r="E212" t="inlineStr">
         <is>
@@ -8065,6 +8280,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I212" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -8083,7 +8299,7 @@
         </is>
       </c>
       <c r="D213" t="n">
-        <v>1710651489</v>
+        <v>1713227659</v>
       </c>
       <c r="E213" t="inlineStr">
         <is>
@@ -8101,6 +8317,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I213" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -8119,7 +8336,7 @@
         </is>
       </c>
       <c r="D214" t="n">
-        <v>1710652686</v>
+        <v>1713229352</v>
       </c>
       <c r="E214" t="inlineStr">
         <is>
@@ -8137,6 +8354,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I214" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -8155,7 +8373,7 @@
         </is>
       </c>
       <c r="D215" t="n">
-        <v>1710716432</v>
+        <v>1713229415</v>
       </c>
       <c r="E215" t="inlineStr">
         <is>
@@ -8173,6 +8391,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I215" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -8191,7 +8410,7 @@
         </is>
       </c>
       <c r="D216" t="n">
-        <v>1710717265</v>
+        <v>1713229683</v>
       </c>
       <c r="E216" t="inlineStr">
         <is>
@@ -8209,6 +8428,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I216" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -8227,7 +8447,7 @@
         </is>
       </c>
       <c r="D217" t="n">
-        <v>1710717309</v>
+        <v>1713229749</v>
       </c>
       <c r="E217" t="inlineStr">
         <is>
@@ -8245,6 +8465,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I217" t="inlineStr"/>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -8263,7 +8484,7 @@
         </is>
       </c>
       <c r="D218" t="n">
-        <v>1710717652</v>
+        <v>1713241438</v>
       </c>
       <c r="E218" t="inlineStr">
         <is>
@@ -8281,6 +8502,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I218" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -8299,7 +8521,7 @@
         </is>
       </c>
       <c r="D219" t="n">
-        <v>1710717678</v>
+        <v>1713241445</v>
       </c>
       <c r="E219" t="inlineStr">
         <is>
@@ -8317,6 +8539,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I219" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -8335,7 +8558,7 @@
         </is>
       </c>
       <c r="D220" t="n">
-        <v>1710725597</v>
+        <v>1713244415</v>
       </c>
       <c r="E220" t="inlineStr">
         <is>
@@ -8353,6 +8576,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I220" t="inlineStr"/>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -8371,7 +8595,7 @@
         </is>
       </c>
       <c r="D221" t="n">
-        <v>1710725611</v>
+        <v>1713244431</v>
       </c>
       <c r="E221" t="inlineStr">
         <is>
@@ -8389,6 +8613,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I221" t="inlineStr"/>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -8407,7 +8632,7 @@
         </is>
       </c>
       <c r="D222" t="n">
-        <v>1710726489</v>
+        <v>1713244475</v>
       </c>
       <c r="E222" t="inlineStr">
         <is>
@@ -8425,6 +8650,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I222" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -8443,7 +8669,7 @@
         </is>
       </c>
       <c r="D223" t="n">
-        <v>1710726498</v>
+        <v>1713244484</v>
       </c>
       <c r="E223" t="inlineStr">
         <is>
@@ -8461,6 +8687,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I223" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -8479,7 +8706,7 @@
         </is>
       </c>
       <c r="D224" t="n">
-        <v>1710728641</v>
+        <v>1713247554</v>
       </c>
       <c r="E224" t="inlineStr">
         <is>
@@ -8497,6 +8724,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I224" t="inlineStr"/>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -8515,7 +8743,7 @@
         </is>
       </c>
       <c r="D225" t="n">
-        <v>1710730614</v>
+        <v>1713247607</v>
       </c>
       <c r="E225" t="inlineStr">
         <is>
@@ -8533,6 +8761,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I225" t="inlineStr"/>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -8551,7 +8780,7 @@
         </is>
       </c>
       <c r="D226" t="n">
-        <v>1710731326</v>
+        <v>1713256453</v>
       </c>
       <c r="E226" t="inlineStr">
         <is>
@@ -8569,6 +8798,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I226" t="inlineStr"/>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -8587,7 +8817,7 @@
         </is>
       </c>
       <c r="D227" t="n">
-        <v>1710731363</v>
+        <v>1713256464</v>
       </c>
       <c r="E227" t="inlineStr">
         <is>
@@ -8605,6 +8835,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I227" t="inlineStr"/>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -8623,7 +8854,7 @@
         </is>
       </c>
       <c r="D228" t="n">
-        <v>1710734346</v>
+        <v>1713315543</v>
       </c>
       <c r="E228" t="inlineStr">
         <is>
@@ -8641,6 +8872,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I228" t="inlineStr"/>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -8659,7 +8891,7 @@
         </is>
       </c>
       <c r="D229" t="n">
-        <v>1710737739</v>
+        <v>1713315596</v>
       </c>
       <c r="E229" t="inlineStr">
         <is>
@@ -8677,6 +8909,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I229" t="inlineStr"/>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -8695,7 +8928,7 @@
         </is>
       </c>
       <c r="D230" t="n">
-        <v>1710737756</v>
+        <v>1713315605</v>
       </c>
       <c r="E230" t="inlineStr">
         <is>
@@ -8713,6 +8946,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I230" t="inlineStr"/>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -8731,7 +8965,7 @@
         </is>
       </c>
       <c r="D231" t="n">
-        <v>1710802029</v>
+        <v>1713315671</v>
       </c>
       <c r="E231" t="inlineStr">
         <is>
@@ -8749,6 +8983,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I231" t="inlineStr"/>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -8767,7 +9002,7 @@
         </is>
       </c>
       <c r="D232" t="n">
-        <v>1710802315</v>
+        <v>1713315729</v>
       </c>
       <c r="E232" t="inlineStr">
         <is>
@@ -8785,6 +9020,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I232" t="inlineStr"/>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -8803,7 +9039,7 @@
         </is>
       </c>
       <c r="D233" t="n">
-        <v>1710802355</v>
+        <v>1713315755</v>
       </c>
       <c r="E233" t="inlineStr">
         <is>
@@ -8821,6 +9057,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I233" t="inlineStr"/>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -8839,7 +9076,7 @@
         </is>
       </c>
       <c r="D234" t="n">
-        <v>1710803487</v>
+        <v>1713325329</v>
       </c>
       <c r="E234" t="inlineStr">
         <is>
@@ -8857,6 +9094,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I234" t="inlineStr"/>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -8875,7 +9113,7 @@
         </is>
       </c>
       <c r="D235" t="n">
-        <v>1710803519</v>
+        <v>1713325341</v>
       </c>
       <c r="E235" t="inlineStr">
         <is>
@@ -8893,6 +9131,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I235" t="inlineStr"/>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -8911,7 +9150,7 @@
         </is>
       </c>
       <c r="D236" t="n">
-        <v>1710814648</v>
+        <v>1713326728</v>
       </c>
       <c r="E236" t="inlineStr">
         <is>
@@ -8929,6 +9168,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I236" t="inlineStr"/>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -8947,7 +9187,7 @@
         </is>
       </c>
       <c r="D237" t="n">
-        <v>1710814658</v>
+        <v>1713326740</v>
       </c>
       <c r="E237" t="inlineStr">
         <is>
@@ -8965,6 +9205,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I237" t="inlineStr"/>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -8983,7 +9224,7 @@
         </is>
       </c>
       <c r="D238" t="n">
-        <v>1710819027</v>
+        <v>1713330431</v>
       </c>
       <c r="E238" t="inlineStr">
         <is>
@@ -9001,6 +9242,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I238" t="inlineStr"/>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -9019,7 +9261,7 @@
         </is>
       </c>
       <c r="D239" t="n">
-        <v>1710820488</v>
+        <v>1713330486</v>
       </c>
       <c r="E239" t="inlineStr">
         <is>
@@ -9037,6 +9279,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I239" t="inlineStr"/>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -9055,7 +9298,7 @@
         </is>
       </c>
       <c r="D240" t="n">
-        <v>1710820500</v>
+        <v>1713332504</v>
       </c>
       <c r="E240" t="inlineStr">
         <is>
@@ -9073,6 +9316,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I240" t="inlineStr"/>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -9091,7 +9335,7 @@
         </is>
       </c>
       <c r="D241" t="n">
-        <v>1710825548</v>
+        <v>1713332583</v>
       </c>
       <c r="E241" t="inlineStr">
         <is>
@@ -9109,6 +9353,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I241" t="inlineStr"/>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -9127,7 +9372,7 @@
         </is>
       </c>
       <c r="D242" t="n">
-        <v>1710829705</v>
+        <v>1713332654</v>
       </c>
       <c r="E242" t="inlineStr">
         <is>
@@ -9145,6 +9390,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I242" t="inlineStr"/>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -9163,7 +9409,7 @@
         </is>
       </c>
       <c r="D243" t="n">
-        <v>1711062126</v>
+        <v>1713332664</v>
       </c>
       <c r="E243" t="inlineStr">
         <is>
@@ -9181,6 +9427,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I243" t="inlineStr"/>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -9199,7 +9446,7 @@
         </is>
       </c>
       <c r="D244" t="n">
-        <v>1711062150</v>
+        <v>1713333262</v>
       </c>
       <c r="E244" t="inlineStr">
         <is>
@@ -9217,6 +9464,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I244" t="inlineStr"/>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -9235,7 +9483,7 @@
         </is>
       </c>
       <c r="D245" t="n">
-        <v>1711062215</v>
+        <v>1713333270</v>
       </c>
       <c r="E245" t="inlineStr">
         <is>
@@ -9253,6 +9501,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I245" t="inlineStr"/>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -9271,7 +9520,7 @@
         </is>
       </c>
       <c r="D246" t="n">
-        <v>1711063462</v>
+        <v>1713399910</v>
       </c>
       <c r="E246" t="inlineStr">
         <is>
@@ -9289,6 +9538,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I246" t="inlineStr"/>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -9307,7 +9557,7 @@
         </is>
       </c>
       <c r="D247" t="n">
-        <v>1711063495</v>
+        <v>1713399969</v>
       </c>
       <c r="E247" t="inlineStr">
         <is>
@@ -9325,6 +9575,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I247" t="inlineStr"/>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -9343,7 +9594,7 @@
         </is>
       </c>
       <c r="D248" t="n">
-        <v>1711070614</v>
+        <v>1713400154</v>
       </c>
       <c r="E248" t="inlineStr">
         <is>
@@ -9361,6 +9612,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I248" t="inlineStr"/>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
@@ -9379,7 +9631,7 @@
         </is>
       </c>
       <c r="D249" t="n">
-        <v>1711070631</v>
+        <v>1713400188</v>
       </c>
       <c r="E249" t="inlineStr">
         <is>
@@ -9397,6 +9649,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I249" t="inlineStr"/>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -9415,7 +9668,7 @@
         </is>
       </c>
       <c r="D250" t="n">
-        <v>1711070643</v>
+        <v>1713401446</v>
       </c>
       <c r="E250" t="inlineStr">
         <is>
@@ -9433,6 +9686,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I250" t="inlineStr"/>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -9451,7 +9705,7 @@
         </is>
       </c>
       <c r="D251" t="n">
-        <v>1711071547</v>
+        <v>1713401498</v>
       </c>
       <c r="E251" t="inlineStr">
         <is>
@@ -9469,6 +9723,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I251" t="inlineStr"/>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
@@ -9487,7 +9742,7 @@
         </is>
       </c>
       <c r="D252" t="n">
-        <v>1711071558</v>
+        <v>1713411301</v>
       </c>
       <c r="E252" t="inlineStr">
         <is>
@@ -9505,6 +9760,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I252" t="inlineStr"/>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
@@ -9523,7 +9779,7 @@
         </is>
       </c>
       <c r="D253" t="n">
-        <v>1711074373</v>
+        <v>1713411311</v>
       </c>
       <c r="E253" t="inlineStr">
         <is>
@@ -9541,6 +9797,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I253" t="inlineStr"/>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
@@ -9559,7 +9816,7 @@
         </is>
       </c>
       <c r="D254" t="n">
-        <v>1711075125</v>
+        <v>1713417265</v>
       </c>
       <c r="E254" t="inlineStr">
         <is>
@@ -9577,6 +9834,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I254" t="inlineStr"/>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -9595,7 +9853,7 @@
         </is>
       </c>
       <c r="D255" t="n">
-        <v>1711075163</v>
+        <v>1713417298</v>
       </c>
       <c r="E255" t="inlineStr">
         <is>
@@ -9613,6 +9871,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I255" t="inlineStr"/>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
@@ -9631,7 +9890,7 @@
         </is>
       </c>
       <c r="D256" t="n">
-        <v>1711075474</v>
+        <v>1713422369</v>
       </c>
       <c r="E256" t="inlineStr">
         <is>
@@ -9649,6 +9908,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I256" t="inlineStr"/>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
@@ -9667,7 +9927,7 @@
         </is>
       </c>
       <c r="D257" t="n">
-        <v>1711075490</v>
+        <v>1713422383</v>
       </c>
       <c r="E257" t="inlineStr">
         <is>
@@ -9685,6 +9945,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I257" t="inlineStr"/>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
@@ -9703,7 +9964,7 @@
         </is>
       </c>
       <c r="D258" t="n">
-        <v>1711078488</v>
+        <v>1713429708</v>
       </c>
       <c r="E258" t="inlineStr">
         <is>
@@ -9721,6 +9982,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I258" t="inlineStr"/>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
@@ -9739,7 +10001,7 @@
         </is>
       </c>
       <c r="D259" t="n">
-        <v>1711078621</v>
+        <v>1713429718</v>
       </c>
       <c r="E259" t="inlineStr">
         <is>
@@ -9757,6 +10019,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I259" t="inlineStr"/>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
@@ -9775,7 +10038,7 @@
         </is>
       </c>
       <c r="D260" t="n">
-        <v>1711079205</v>
+        <v>1713429819</v>
       </c>
       <c r="E260" t="inlineStr">
         <is>
@@ -9793,6 +10056,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I260" t="inlineStr"/>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
@@ -9811,7 +10075,7 @@
         </is>
       </c>
       <c r="D261" t="n">
-        <v>1711082456</v>
+        <v>1713429828</v>
       </c>
       <c r="E261" t="inlineStr">
         <is>
@@ -9829,6 +10093,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I261" t="inlineStr"/>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
@@ -9847,7 +10112,7 @@
         </is>
       </c>
       <c r="D262" t="n">
-        <v>1711082469</v>
+        <v>1713488043</v>
       </c>
       <c r="E262" t="inlineStr">
         <is>
@@ -9865,6 +10130,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I262" t="inlineStr"/>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
@@ -9883,7 +10149,7 @@
         </is>
       </c>
       <c r="D263" t="n">
-        <v>1711148564</v>
+        <v>1713488074</v>
       </c>
       <c r="E263" t="inlineStr">
         <is>
@@ -9901,6 +10167,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I263" t="inlineStr"/>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
@@ -9919,7 +10186,7 @@
         </is>
       </c>
       <c r="D264" t="n">
-        <v>1711148617</v>
+        <v>1713488312</v>
       </c>
       <c r="E264" t="inlineStr">
         <is>
@@ -9937,6 +10204,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I264" t="inlineStr"/>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
@@ -9955,7 +10223,7 @@
         </is>
       </c>
       <c r="D265" t="n">
-        <v>1711148645</v>
+        <v>1713488384</v>
       </c>
       <c r="E265" t="inlineStr">
         <is>
@@ -9973,6 +10241,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I265" t="inlineStr"/>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
@@ -9991,7 +10260,7 @@
         </is>
       </c>
       <c r="D266" t="n">
-        <v>1711149548</v>
+        <v>1713488534</v>
       </c>
       <c r="E266" t="inlineStr">
         <is>
@@ -10009,6 +10278,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I266" t="inlineStr"/>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
@@ -10027,7 +10297,7 @@
         </is>
       </c>
       <c r="D267" t="n">
-        <v>1711149594</v>
+        <v>1713488593</v>
       </c>
       <c r="E267" t="inlineStr">
         <is>
@@ -10045,6 +10315,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I267" t="inlineStr"/>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
@@ -10063,7 +10334,7 @@
         </is>
       </c>
       <c r="D268" t="n">
-        <v>1711160535</v>
+        <v>1713502916</v>
       </c>
       <c r="E268" t="inlineStr">
         <is>
@@ -10081,6 +10352,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I268" t="inlineStr"/>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
@@ -10099,7 +10371,7 @@
         </is>
       </c>
       <c r="D269" t="n">
-        <v>1711160558</v>
+        <v>1713502927</v>
       </c>
       <c r="E269" t="inlineStr">
         <is>
@@ -10117,6 +10389,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I269" t="inlineStr"/>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
@@ -10135,7 +10408,7 @@
         </is>
       </c>
       <c r="D270" t="n">
-        <v>1711162141</v>
+        <v>1713512430</v>
       </c>
       <c r="E270" t="inlineStr">
         <is>
@@ -10153,6 +10426,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I270" t="inlineStr"/>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
@@ -10171,7 +10445,7 @@
         </is>
       </c>
       <c r="D271" t="n">
-        <v>1711162156</v>
+        <v>1713512439</v>
       </c>
       <c r="E271" t="inlineStr">
         <is>
@@ -10189,6 +10463,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I271" t="inlineStr"/>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
@@ -10207,7 +10482,7 @@
         </is>
       </c>
       <c r="D272" t="n">
-        <v>1711162166</v>
+        <v>1713516905</v>
       </c>
       <c r="E272" t="inlineStr">
         <is>
@@ -10225,6 +10500,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I272" t="inlineStr"/>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
@@ -10243,7 +10519,7 @@
         </is>
       </c>
       <c r="D273" t="n">
-        <v>1711168626</v>
+        <v>1713516918</v>
       </c>
       <c r="E273" t="inlineStr">
         <is>
@@ -10261,6 +10537,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I273" t="inlineStr"/>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
@@ -10279,7 +10556,7 @@
         </is>
       </c>
       <c r="D274" t="n">
-        <v>1711169035</v>
+        <v>1713590124</v>
       </c>
       <c r="E274" t="inlineStr">
         <is>
@@ -10297,6 +10574,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I274" t="inlineStr"/>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
@@ -10315,7 +10593,7 @@
         </is>
       </c>
       <c r="D275" t="n">
-        <v>1711237159</v>
+        <v>1713590192</v>
       </c>
       <c r="E275" t="inlineStr">
         <is>
@@ -10333,6 +10611,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I275" t="inlineStr"/>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
@@ -10351,7 +10630,7 @@
         </is>
       </c>
       <c r="D276" t="n">
-        <v>1711237324</v>
+        <v>1713599785</v>
       </c>
       <c r="E276" t="inlineStr">
         <is>
@@ -10369,6 +10648,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I276" t="inlineStr"/>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
@@ -10387,7 +10667,7 @@
         </is>
       </c>
       <c r="D277" t="n">
-        <v>1711237358</v>
+        <v>1713599793</v>
       </c>
       <c r="E277" t="inlineStr">
         <is>
@@ -10405,6 +10685,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I277" t="inlineStr"/>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
@@ -10423,7 +10704,7 @@
         </is>
       </c>
       <c r="D278" t="n">
-        <v>1711237498</v>
+        <v>1713744879</v>
       </c>
       <c r="E278" t="inlineStr">
         <is>
@@ -10441,6 +10722,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I278" t="inlineStr"/>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
@@ -10459,7 +10741,7 @@
         </is>
       </c>
       <c r="D279" t="n">
-        <v>1711237561</v>
+        <v>1713744935</v>
       </c>
       <c r="E279" t="inlineStr">
         <is>
@@ -10477,6 +10759,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I279" t="inlineStr"/>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
@@ -10495,7 +10778,7 @@
         </is>
       </c>
       <c r="D280" t="n">
-        <v>1711246163</v>
+        <v>1713745585</v>
       </c>
       <c r="E280" t="inlineStr">
         <is>
@@ -10513,6 +10796,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I280" t="inlineStr"/>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
@@ -10531,7 +10815,7 @@
         </is>
       </c>
       <c r="D281" t="n">
-        <v>1711246171</v>
+        <v>1713745654</v>
       </c>
       <c r="E281" t="inlineStr">
         <is>
@@ -10549,6 +10833,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I281" t="inlineStr"/>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
@@ -10567,7 +10852,7 @@
         </is>
       </c>
       <c r="D282" t="n">
-        <v>1711246182</v>
+        <v>1713746535</v>
       </c>
       <c r="E282" t="inlineStr">
         <is>
@@ -10585,6 +10870,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I282" t="inlineStr"/>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
@@ -10603,7 +10889,7 @@
         </is>
       </c>
       <c r="D283" t="n">
-        <v>1711246727</v>
+        <v>1713746602</v>
       </c>
       <c r="E283" t="inlineStr">
         <is>
@@ -10621,6 +10907,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I283" t="inlineStr"/>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
@@ -10639,7 +10926,7 @@
         </is>
       </c>
       <c r="D284" t="n">
-        <v>1711246742</v>
+        <v>1713761973</v>
       </c>
       <c r="E284" t="inlineStr">
         <is>
@@ -10657,6 +10944,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I284" t="inlineStr"/>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
@@ -10675,7 +10963,7 @@
         </is>
       </c>
       <c r="D285" t="n">
-        <v>1711250641</v>
+        <v>1713761979</v>
       </c>
       <c r="E285" t="inlineStr">
         <is>
@@ -10693,6 +10981,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I285" t="inlineStr"/>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
@@ -10711,7 +11000,7 @@
         </is>
       </c>
       <c r="D286" t="n">
-        <v>1711250896</v>
+        <v>1713762460</v>
       </c>
       <c r="E286" t="inlineStr">
         <is>
@@ -10729,6 +11018,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I286" t="inlineStr"/>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
@@ -10747,7 +11037,7 @@
         </is>
       </c>
       <c r="D287" t="n">
-        <v>1711250958</v>
+        <v>1713762471</v>
       </c>
       <c r="E287" t="inlineStr">
         <is>
@@ -10765,6 +11055,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I287" t="inlineStr"/>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
@@ -10783,7 +11074,7 @@
         </is>
       </c>
       <c r="D288" t="n">
-        <v>1711252499</v>
+        <v>1713772190</v>
       </c>
       <c r="E288" t="inlineStr">
         <is>
@@ -10801,6 +11092,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I288" t="inlineStr"/>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
@@ -10819,7 +11111,7 @@
         </is>
       </c>
       <c r="D289" t="n">
-        <v>1711252506</v>
+        <v>1713772201</v>
       </c>
       <c r="E289" t="inlineStr">
         <is>
@@ -10837,6 +11129,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I289" t="inlineStr"/>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
@@ -10855,7 +11148,7 @@
         </is>
       </c>
       <c r="D290" t="n">
-        <v>1711257295</v>
+        <v>1713833446</v>
       </c>
       <c r="E290" t="inlineStr">
         <is>
@@ -10873,6 +11166,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I290" t="inlineStr"/>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
@@ -10891,7 +11185,7 @@
         </is>
       </c>
       <c r="D291" t="n">
-        <v>1711257894</v>
+        <v>1713833498</v>
       </c>
       <c r="E291" t="inlineStr">
         <is>
@@ -10909,6 +11203,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I291" t="inlineStr"/>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
@@ -10927,7 +11222,7 @@
         </is>
       </c>
       <c r="D292" t="n">
-        <v>1711258046</v>
+        <v>1713833672</v>
       </c>
       <c r="E292" t="inlineStr">
         <is>
@@ -10945,6 +11240,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I292" t="inlineStr"/>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
@@ -10963,7 +11259,7 @@
         </is>
       </c>
       <c r="D293" t="n">
-        <v>1711259717</v>
+        <v>1713833718</v>
       </c>
       <c r="E293" t="inlineStr">
         <is>
@@ -10981,6 +11277,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I293" t="inlineStr"/>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
@@ -10999,7 +11296,7 @@
         </is>
       </c>
       <c r="D294" t="n">
-        <v>1711259740</v>
+        <v>1713833774</v>
       </c>
       <c r="E294" t="inlineStr">
         <is>
@@ -11017,6 +11314,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I294" t="inlineStr"/>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
@@ -11035,7 +11333,7 @@
         </is>
       </c>
       <c r="D295" t="n">
-        <v>1711323645</v>
+        <v>1713833847</v>
       </c>
       <c r="E295" t="inlineStr">
         <is>
@@ -11053,6 +11351,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I295" t="inlineStr"/>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
@@ -11071,7 +11370,7 @@
         </is>
       </c>
       <c r="D296" t="n">
-        <v>1711323871</v>
+        <v>1713843460</v>
       </c>
       <c r="E296" t="inlineStr">
         <is>
@@ -11089,6 +11388,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I296" t="inlineStr"/>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
@@ -11107,7 +11407,7 @@
         </is>
       </c>
       <c r="D297" t="n">
-        <v>1711323925</v>
+        <v>1713843467</v>
       </c>
       <c r="E297" t="inlineStr">
         <is>
@@ -11125,6 +11425,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I297" t="inlineStr"/>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
@@ -11143,7 +11444,7 @@
         </is>
       </c>
       <c r="D298" t="n">
-        <v>1711324658</v>
+        <v>1713849476</v>
       </c>
       <c r="E298" t="inlineStr">
         <is>
@@ -11161,6 +11462,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I298" t="inlineStr"/>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
@@ -11179,7 +11481,7 @@
         </is>
       </c>
       <c r="D299" t="n">
-        <v>1711324726</v>
+        <v>1713849533</v>
       </c>
       <c r="E299" t="inlineStr">
         <is>
@@ -11197,6 +11499,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I299" t="inlineStr"/>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
@@ -11215,7 +11518,7 @@
         </is>
       </c>
       <c r="D300" t="n">
-        <v>1711332375</v>
+        <v>1713850131</v>
       </c>
       <c r="E300" t="inlineStr">
         <is>
@@ -11233,6 +11536,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I300" t="inlineStr"/>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
@@ -11251,7 +11555,7 @@
         </is>
       </c>
       <c r="D301" t="n">
-        <v>1711332390</v>
+        <v>1713850139</v>
       </c>
       <c r="E301" t="inlineStr">
         <is>
@@ -11269,6 +11573,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I301" t="inlineStr"/>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
@@ -11287,7 +11592,7 @@
         </is>
       </c>
       <c r="D302" t="n">
-        <v>1711332398</v>
+        <v>1713856071</v>
       </c>
       <c r="E302" t="inlineStr">
         <is>
@@ -11305,6 +11610,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I302" t="inlineStr"/>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
@@ -11323,7 +11629,7 @@
         </is>
       </c>
       <c r="D303" t="n">
-        <v>1711334902</v>
+        <v>1713856082</v>
       </c>
       <c r="E303" t="inlineStr">
         <is>
@@ -11341,6 +11647,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I303" t="inlineStr"/>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
@@ -11359,7 +11666,7 @@
         </is>
       </c>
       <c r="D304" t="n">
-        <v>1711334914</v>
+        <v>1713856864</v>
       </c>
       <c r="E304" t="inlineStr">
         <is>
@@ -11377,6 +11684,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I304" t="inlineStr"/>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
@@ -11395,7 +11703,7 @@
         </is>
       </c>
       <c r="D305" t="n">
-        <v>1711336716</v>
+        <v>1713856873</v>
       </c>
       <c r="E305" t="inlineStr">
         <is>
@@ -11413,6 +11721,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I305" t="inlineStr"/>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
@@ -11431,7 +11740,7 @@
         </is>
       </c>
       <c r="D306" t="n">
-        <v>1711338880</v>
+        <v>1713918637</v>
       </c>
       <c r="E306" t="inlineStr">
         <is>
@@ -11449,6 +11758,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I306" t="inlineStr"/>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
@@ -11467,7 +11777,7 @@
         </is>
       </c>
       <c r="D307" t="n">
-        <v>1711338901</v>
+        <v>1713918706</v>
       </c>
       <c r="E307" t="inlineStr">
         <is>
@@ -11485,6 +11795,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I307" t="inlineStr"/>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
@@ -11503,7 +11814,7 @@
         </is>
       </c>
       <c r="D308" t="n">
-        <v>1711339771</v>
+        <v>1713919385</v>
       </c>
       <c r="E308" t="inlineStr">
         <is>
@@ -11521,6 +11832,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I308" t="inlineStr"/>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
@@ -11539,7 +11851,7 @@
         </is>
       </c>
       <c r="D309" t="n">
-        <v>1711342532</v>
+        <v>1713919411</v>
       </c>
       <c r="E309" t="inlineStr">
         <is>
@@ -11557,6 +11869,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I309" t="inlineStr"/>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
@@ -11575,7 +11888,7 @@
         </is>
       </c>
       <c r="D310" t="n">
-        <v>1711342895</v>
+        <v>1713920856</v>
       </c>
       <c r="E310" t="inlineStr">
         <is>
@@ -11593,6 +11906,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I310" t="inlineStr"/>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
@@ -11611,7 +11925,7 @@
         </is>
       </c>
       <c r="D311" t="n">
-        <v>1711414077</v>
+        <v>1713920930</v>
       </c>
       <c r="E311" t="inlineStr">
         <is>
@@ -11629,6 +11943,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I311" t="inlineStr"/>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
@@ -11647,7 +11962,7 @@
         </is>
       </c>
       <c r="D312" t="n">
-        <v>1711415002</v>
+        <v>1713934765</v>
       </c>
       <c r="E312" t="inlineStr">
         <is>
@@ -11665,6 +11980,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I312" t="inlineStr"/>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
@@ -11683,7 +11999,7 @@
         </is>
       </c>
       <c r="D313" t="n">
-        <v>1711415032</v>
+        <v>1713934774</v>
       </c>
       <c r="E313" t="inlineStr">
         <is>
@@ -11701,6 +12017,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I313" t="inlineStr"/>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
@@ -11719,7 +12036,7 @@
         </is>
       </c>
       <c r="D314" t="n">
-        <v>1711415672</v>
+        <v>1713941575</v>
       </c>
       <c r="E314" t="inlineStr">
         <is>
@@ -11737,6 +12054,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I314" t="inlineStr"/>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
@@ -11755,7 +12073,7 @@
         </is>
       </c>
       <c r="D315" t="n">
-        <v>1711415738</v>
+        <v>1713941586</v>
       </c>
       <c r="E315" t="inlineStr">
         <is>
@@ -11773,6 +12091,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I315" t="inlineStr"/>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
@@ -11791,7 +12110,7 @@
         </is>
       </c>
       <c r="D316" t="n">
-        <v>1711426025</v>
+        <v>1713944737</v>
       </c>
       <c r="E316" t="inlineStr">
         <is>
@@ -11809,6 +12128,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I316" t="inlineStr"/>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
@@ -11827,7 +12147,7 @@
         </is>
       </c>
       <c r="D317" t="n">
-        <v>1711426034</v>
+        <v>1713944747</v>
       </c>
       <c r="E317" t="inlineStr">
         <is>
@@ -11845,6 +12165,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I317" t="inlineStr"/>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
@@ -11863,7 +12184,7 @@
         </is>
       </c>
       <c r="D318" t="n">
-        <v>1711431645</v>
+        <v>1714006270</v>
       </c>
       <c r="E318" t="inlineStr">
         <is>
@@ -11881,6 +12202,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I318" t="inlineStr"/>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
@@ -11899,7 +12221,7 @@
         </is>
       </c>
       <c r="D319" t="n">
-        <v>1711431685</v>
+        <v>1714006335</v>
       </c>
       <c r="E319" t="inlineStr">
         <is>
@@ -11917,6 +12239,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I319" t="inlineStr"/>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
@@ -11935,7 +12258,7 @@
         </is>
       </c>
       <c r="D320" t="n">
-        <v>1711435389</v>
+        <v>1714006685</v>
       </c>
       <c r="E320" t="inlineStr">
         <is>
@@ -11953,6 +12276,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I320" t="inlineStr"/>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
@@ -11971,7 +12295,7 @@
         </is>
       </c>
       <c r="D321" t="n">
-        <v>1711435396</v>
+        <v>1714006745</v>
       </c>
       <c r="E321" t="inlineStr">
         <is>
@@ -11989,6 +12313,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I321" t="inlineStr"/>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
@@ -12007,7 +12332,7 @@
         </is>
       </c>
       <c r="D322" t="n">
-        <v>1711438555</v>
+        <v>1714007063</v>
       </c>
       <c r="E322" t="inlineStr">
         <is>
@@ -12025,6 +12350,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I322" t="inlineStr"/>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
@@ -12043,7 +12369,7 @@
         </is>
       </c>
       <c r="D323" t="n">
-        <v>1711438566</v>
+        <v>1714007102</v>
       </c>
       <c r="E323" t="inlineStr">
         <is>
@@ -12061,6 +12387,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I323" t="inlineStr"/>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
@@ -12079,7 +12406,7 @@
         </is>
       </c>
       <c r="D324" t="n">
-        <v>1711438592</v>
+        <v>1714017056</v>
       </c>
       <c r="E324" t="inlineStr">
         <is>
@@ -12097,6 +12424,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I324" t="inlineStr"/>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
@@ -12115,7 +12443,7 @@
         </is>
       </c>
       <c r="D325" t="n">
-        <v>1711441354</v>
+        <v>1714017064</v>
       </c>
       <c r="E325" t="inlineStr">
         <is>
@@ -12133,6 +12461,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I325" t="inlineStr"/>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
@@ -12151,7 +12480,7 @@
         </is>
       </c>
       <c r="D326" t="n">
-        <v>1711442542</v>
+        <v>1714017423</v>
       </c>
       <c r="E326" t="inlineStr">
         <is>
@@ -12169,6 +12498,1450 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I326" t="inlineStr"/>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>Door_Operation</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>LivingRoom</t>
+        </is>
+      </c>
+      <c r="D327" t="n">
+        <v>1714017428</v>
+      </c>
+      <c r="E327" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F327" t="inlineStr"/>
+      <c r="G327" t="inlineStr">
+        <is>
+          <t>LivingRoom.Door001.state: close</t>
+        </is>
+      </c>
+      <c r="H327" t="inlineStr">
+        <is>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I327" t="inlineStr"/>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>Door_Operation</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>LivingRoom</t>
+        </is>
+      </c>
+      <c r="D328" t="n">
+        <v>1714021549</v>
+      </c>
+      <c r="E328" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F328" t="inlineStr"/>
+      <c r="G328" t="inlineStr">
+        <is>
+          <t>LivingRoom.Door001.state: open</t>
+        </is>
+      </c>
+      <c r="H328" t="inlineStr">
+        <is>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I328" t="inlineStr"/>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>Door_Operation</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>LivingRoom</t>
+        </is>
+      </c>
+      <c r="D329" t="n">
+        <v>1714021557</v>
+      </c>
+      <c r="E329" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F329" t="inlineStr"/>
+      <c r="G329" t="inlineStr">
+        <is>
+          <t>LivingRoom.Door001.state: close</t>
+        </is>
+      </c>
+      <c r="H329" t="inlineStr">
+        <is>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I329" t="inlineStr"/>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>Door_Operation</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>LivingRoom</t>
+        </is>
+      </c>
+      <c r="D330" t="n">
+        <v>1714022155</v>
+      </c>
+      <c r="E330" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F330" t="inlineStr"/>
+      <c r="G330" t="inlineStr">
+        <is>
+          <t>LivingRoom.Door001.state: open</t>
+        </is>
+      </c>
+      <c r="H330" t="inlineStr">
+        <is>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I330" t="inlineStr"/>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>Door_Operation</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>LivingRoom</t>
+        </is>
+      </c>
+      <c r="D331" t="n">
+        <v>1714022207</v>
+      </c>
+      <c r="E331" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F331" t="inlineStr"/>
+      <c r="G331" t="inlineStr">
+        <is>
+          <t>LivingRoom.Door001.state: close</t>
+        </is>
+      </c>
+      <c r="H331" t="inlineStr">
+        <is>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I331" t="inlineStr"/>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>Door_Operation</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>LivingRoom</t>
+        </is>
+      </c>
+      <c r="D332" t="n">
+        <v>1714022382</v>
+      </c>
+      <c r="E332" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F332" t="inlineStr"/>
+      <c r="G332" t="inlineStr">
+        <is>
+          <t>LivingRoom.Door001.state: open</t>
+        </is>
+      </c>
+      <c r="H332" t="inlineStr">
+        <is>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I332" t="inlineStr"/>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>Door_Operation</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>LivingRoom</t>
+        </is>
+      </c>
+      <c r="D333" t="n">
+        <v>1714022427</v>
+      </c>
+      <c r="E333" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F333" t="inlineStr"/>
+      <c r="G333" t="inlineStr">
+        <is>
+          <t>LivingRoom.Door001.state: close</t>
+        </is>
+      </c>
+      <c r="H333" t="inlineStr">
+        <is>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I333" t="inlineStr"/>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>Door_Operation</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>LivingRoom</t>
+        </is>
+      </c>
+      <c r="D334" t="n">
+        <v>1714026445</v>
+      </c>
+      <c r="E334" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F334" t="inlineStr"/>
+      <c r="G334" t="inlineStr">
+        <is>
+          <t>LivingRoom.Door001.state: open</t>
+        </is>
+      </c>
+      <c r="H334" t="inlineStr">
+        <is>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I334" t="inlineStr"/>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>Door_Operation</t>
+        </is>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>LivingRoom</t>
+        </is>
+      </c>
+      <c r="D335" t="n">
+        <v>1714026457</v>
+      </c>
+      <c r="E335" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F335" t="inlineStr"/>
+      <c r="G335" t="inlineStr">
+        <is>
+          <t>LivingRoom.Door001.state: close</t>
+        </is>
+      </c>
+      <c r="H335" t="inlineStr">
+        <is>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I335" t="inlineStr"/>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>Door_Operation</t>
+        </is>
+      </c>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>LivingRoom</t>
+        </is>
+      </c>
+      <c r="D336" t="n">
+        <v>1714034268</v>
+      </c>
+      <c r="E336" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F336" t="inlineStr"/>
+      <c r="G336" t="inlineStr">
+        <is>
+          <t>LivingRoom.Door001.state: open</t>
+        </is>
+      </c>
+      <c r="H336" t="inlineStr">
+        <is>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I336" t="inlineStr"/>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>Door_Operation</t>
+        </is>
+      </c>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>LivingRoom</t>
+        </is>
+      </c>
+      <c r="D337" t="n">
+        <v>1714034276</v>
+      </c>
+      <c r="E337" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F337" t="inlineStr"/>
+      <c r="G337" t="inlineStr">
+        <is>
+          <t>LivingRoom.Door001.state: close</t>
+        </is>
+      </c>
+      <c r="H337" t="inlineStr">
+        <is>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I337" t="inlineStr"/>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>Door_Operation</t>
+        </is>
+      </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>LivingRoom</t>
+        </is>
+      </c>
+      <c r="D338" t="n">
+        <v>1714091526</v>
+      </c>
+      <c r="E338" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F338" t="inlineStr"/>
+      <c r="G338" t="inlineStr">
+        <is>
+          <t>LivingRoom.Door001.state: open</t>
+        </is>
+      </c>
+      <c r="H338" t="inlineStr">
+        <is>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I338" t="inlineStr"/>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>Door_Operation</t>
+        </is>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>LivingRoom</t>
+        </is>
+      </c>
+      <c r="D339" t="n">
+        <v>1714091607</v>
+      </c>
+      <c r="E339" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F339" t="inlineStr"/>
+      <c r="G339" t="inlineStr">
+        <is>
+          <t>LivingRoom.Door001.state: close</t>
+        </is>
+      </c>
+      <c r="H339" t="inlineStr">
+        <is>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I339" t="inlineStr"/>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>Door_Operation</t>
+        </is>
+      </c>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>LivingRoom</t>
+        </is>
+      </c>
+      <c r="D340" t="n">
+        <v>1714092302</v>
+      </c>
+      <c r="E340" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F340" t="inlineStr"/>
+      <c r="G340" t="inlineStr">
+        <is>
+          <t>LivingRoom.Door001.state: open</t>
+        </is>
+      </c>
+      <c r="H340" t="inlineStr">
+        <is>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I340" t="inlineStr"/>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>Door_Operation</t>
+        </is>
+      </c>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>LivingRoom</t>
+        </is>
+      </c>
+      <c r="D341" t="n">
+        <v>1714092337</v>
+      </c>
+      <c r="E341" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F341" t="inlineStr"/>
+      <c r="G341" t="inlineStr">
+        <is>
+          <t>LivingRoom.Door001.state: close</t>
+        </is>
+      </c>
+      <c r="H341" t="inlineStr">
+        <is>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I341" t="inlineStr"/>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>Door_Operation</t>
+        </is>
+      </c>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t>LivingRoom</t>
+        </is>
+      </c>
+      <c r="D342" t="n">
+        <v>1714092932</v>
+      </c>
+      <c r="E342" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F342" t="inlineStr"/>
+      <c r="G342" t="inlineStr">
+        <is>
+          <t>LivingRoom.Door001.state: open</t>
+        </is>
+      </c>
+      <c r="H342" t="inlineStr">
+        <is>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I342" t="inlineStr"/>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>Door_Operation</t>
+        </is>
+      </c>
+      <c r="C343" t="inlineStr">
+        <is>
+          <t>LivingRoom</t>
+        </is>
+      </c>
+      <c r="D343" t="n">
+        <v>1714092977</v>
+      </c>
+      <c r="E343" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F343" t="inlineStr"/>
+      <c r="G343" t="inlineStr">
+        <is>
+          <t>LivingRoom.Door001.state: close</t>
+        </is>
+      </c>
+      <c r="H343" t="inlineStr">
+        <is>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I343" t="inlineStr"/>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>Door_Operation</t>
+        </is>
+      </c>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>LivingRoom</t>
+        </is>
+      </c>
+      <c r="D344" t="n">
+        <v>1714103456</v>
+      </c>
+      <c r="E344" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F344" t="inlineStr"/>
+      <c r="G344" t="inlineStr">
+        <is>
+          <t>LivingRoom.Door001.state: open</t>
+        </is>
+      </c>
+      <c r="H344" t="inlineStr">
+        <is>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I344" t="inlineStr"/>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>Door_Operation</t>
+        </is>
+      </c>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t>LivingRoom</t>
+        </is>
+      </c>
+      <c r="D345" t="n">
+        <v>1714103464</v>
+      </c>
+      <c r="E345" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F345" t="inlineStr"/>
+      <c r="G345" t="inlineStr">
+        <is>
+          <t>LivingRoom.Door001.state: close</t>
+        </is>
+      </c>
+      <c r="H345" t="inlineStr">
+        <is>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I345" t="inlineStr"/>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>Door_Operation</t>
+        </is>
+      </c>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>LivingRoom</t>
+        </is>
+      </c>
+      <c r="D346" t="n">
+        <v>1714109445</v>
+      </c>
+      <c r="E346" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F346" t="inlineStr"/>
+      <c r="G346" t="inlineStr">
+        <is>
+          <t>LivingRoom.Door001.state: open</t>
+        </is>
+      </c>
+      <c r="H346" t="inlineStr">
+        <is>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I346" t="inlineStr"/>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>Door_Operation</t>
+        </is>
+      </c>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>LivingRoom</t>
+        </is>
+      </c>
+      <c r="D347" t="n">
+        <v>1714109503</v>
+      </c>
+      <c r="E347" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F347" t="inlineStr"/>
+      <c r="G347" t="inlineStr">
+        <is>
+          <t>LivingRoom.Door001.state: close</t>
+        </is>
+      </c>
+      <c r="H347" t="inlineStr">
+        <is>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I347" t="inlineStr"/>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>Door_Operation</t>
+        </is>
+      </c>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t>LivingRoom</t>
+        </is>
+      </c>
+      <c r="D348" t="n">
+        <v>1714109984</v>
+      </c>
+      <c r="E348" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F348" t="inlineStr"/>
+      <c r="G348" t="inlineStr">
+        <is>
+          <t>LivingRoom.Door001.state: open</t>
+        </is>
+      </c>
+      <c r="H348" t="inlineStr">
+        <is>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I348" t="inlineStr"/>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>Door_Operation</t>
+        </is>
+      </c>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t>LivingRoom</t>
+        </is>
+      </c>
+      <c r="D349" t="n">
+        <v>1714109994</v>
+      </c>
+      <c r="E349" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F349" t="inlineStr"/>
+      <c r="G349" t="inlineStr">
+        <is>
+          <t>LivingRoom.Door001.state: close</t>
+        </is>
+      </c>
+      <c r="H349" t="inlineStr">
+        <is>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I349" t="inlineStr"/>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>Door_Operation</t>
+        </is>
+      </c>
+      <c r="C350" t="inlineStr">
+        <is>
+          <t>LivingRoom</t>
+        </is>
+      </c>
+      <c r="D350" t="n">
+        <v>1714118043</v>
+      </c>
+      <c r="E350" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F350" t="inlineStr"/>
+      <c r="G350" t="inlineStr">
+        <is>
+          <t>LivingRoom.Door001.state: open</t>
+        </is>
+      </c>
+      <c r="H350" t="inlineStr">
+        <is>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I350" t="inlineStr"/>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>Door_Operation</t>
+        </is>
+      </c>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t>LivingRoom</t>
+        </is>
+      </c>
+      <c r="D351" t="n">
+        <v>1714118052</v>
+      </c>
+      <c r="E351" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F351" t="inlineStr"/>
+      <c r="G351" t="inlineStr">
+        <is>
+          <t>LivingRoom.Door001.state: close</t>
+        </is>
+      </c>
+      <c r="H351" t="inlineStr">
+        <is>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I351" t="inlineStr"/>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>Door_Operation</t>
+        </is>
+      </c>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t>LivingRoom</t>
+        </is>
+      </c>
+      <c r="D352" t="n">
+        <v>1714118499</v>
+      </c>
+      <c r="E352" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F352" t="inlineStr"/>
+      <c r="G352" t="inlineStr">
+        <is>
+          <t>LivingRoom.Door001.state: open</t>
+        </is>
+      </c>
+      <c r="H352" t="inlineStr">
+        <is>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I352" t="inlineStr"/>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>Door_Operation</t>
+        </is>
+      </c>
+      <c r="C353" t="inlineStr">
+        <is>
+          <t>LivingRoom</t>
+        </is>
+      </c>
+      <c r="D353" t="n">
+        <v>1714118510</v>
+      </c>
+      <c r="E353" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F353" t="inlineStr"/>
+      <c r="G353" t="inlineStr">
+        <is>
+          <t>LivingRoom.Door001.state: close</t>
+        </is>
+      </c>
+      <c r="H353" t="inlineStr">
+        <is>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I353" t="inlineStr"/>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>Door_Operation</t>
+        </is>
+      </c>
+      <c r="C354" t="inlineStr">
+        <is>
+          <t>LivingRoom</t>
+        </is>
+      </c>
+      <c r="D354" t="n">
+        <v>1714192167</v>
+      </c>
+      <c r="E354" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F354" t="inlineStr"/>
+      <c r="G354" t="inlineStr">
+        <is>
+          <t>LivingRoom.Door001.state: open</t>
+        </is>
+      </c>
+      <c r="H354" t="inlineStr">
+        <is>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I354" t="inlineStr"/>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>Door_Operation</t>
+        </is>
+      </c>
+      <c r="C355" t="inlineStr">
+        <is>
+          <t>LivingRoom</t>
+        </is>
+      </c>
+      <c r="D355" t="n">
+        <v>1714192234</v>
+      </c>
+      <c r="E355" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F355" t="inlineStr"/>
+      <c r="G355" t="inlineStr">
+        <is>
+          <t>LivingRoom.Door001.state: close</t>
+        </is>
+      </c>
+      <c r="H355" t="inlineStr">
+        <is>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I355" t="inlineStr"/>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>Door_Operation</t>
+        </is>
+      </c>
+      <c r="C356" t="inlineStr">
+        <is>
+          <t>LivingRoom</t>
+        </is>
+      </c>
+      <c r="D356" t="n">
+        <v>1714196874</v>
+      </c>
+      <c r="E356" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F356" t="inlineStr"/>
+      <c r="G356" t="inlineStr">
+        <is>
+          <t>LivingRoom.Door001.state: open</t>
+        </is>
+      </c>
+      <c r="H356" t="inlineStr">
+        <is>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I356" t="inlineStr"/>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>Door_Operation</t>
+        </is>
+      </c>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t>LivingRoom</t>
+        </is>
+      </c>
+      <c r="D357" t="n">
+        <v>1714196906</v>
+      </c>
+      <c r="E357" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F357" t="inlineStr"/>
+      <c r="G357" t="inlineStr">
+        <is>
+          <t>LivingRoom.Door001.state: close</t>
+        </is>
+      </c>
+      <c r="H357" t="inlineStr">
+        <is>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I357" t="inlineStr"/>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>Door_Operation</t>
+        </is>
+      </c>
+      <c r="C358" t="inlineStr">
+        <is>
+          <t>LivingRoom</t>
+        </is>
+      </c>
+      <c r="D358" t="n">
+        <v>1714201723</v>
+      </c>
+      <c r="E358" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F358" t="inlineStr"/>
+      <c r="G358" t="inlineStr">
+        <is>
+          <t>LivingRoom.Door001.state: open</t>
+        </is>
+      </c>
+      <c r="H358" t="inlineStr">
+        <is>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I358" t="inlineStr"/>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>Door_Operation</t>
+        </is>
+      </c>
+      <c r="C359" t="inlineStr">
+        <is>
+          <t>LivingRoom</t>
+        </is>
+      </c>
+      <c r="D359" t="n">
+        <v>1714201729</v>
+      </c>
+      <c r="E359" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F359" t="inlineStr"/>
+      <c r="G359" t="inlineStr">
+        <is>
+          <t>LivingRoom.Door001.state: close</t>
+        </is>
+      </c>
+      <c r="H359" t="inlineStr">
+        <is>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I359" t="inlineStr"/>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>Door_Operation</t>
+        </is>
+      </c>
+      <c r="C360" t="inlineStr">
+        <is>
+          <t>LivingRoom</t>
+        </is>
+      </c>
+      <c r="D360" t="n">
+        <v>1714206647</v>
+      </c>
+      <c r="E360" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F360" t="inlineStr"/>
+      <c r="G360" t="inlineStr">
+        <is>
+          <t>LivingRoom.Door001.state: open</t>
+        </is>
+      </c>
+      <c r="H360" t="inlineStr">
+        <is>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I360" t="inlineStr"/>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>Door_Operation</t>
+        </is>
+      </c>
+      <c r="C361" t="inlineStr">
+        <is>
+          <t>LivingRoom</t>
+        </is>
+      </c>
+      <c r="D361" t="n">
+        <v>1714206656</v>
+      </c>
+      <c r="E361" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F361" t="inlineStr"/>
+      <c r="G361" t="inlineStr">
+        <is>
+          <t>LivingRoom.Door001.state: close</t>
+        </is>
+      </c>
+      <c r="H361" t="inlineStr">
+        <is>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I361" t="inlineStr"/>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>Door_Operation</t>
+        </is>
+      </c>
+      <c r="C362" t="inlineStr">
+        <is>
+          <t>LivingRoom</t>
+        </is>
+      </c>
+      <c r="D362" t="n">
+        <v>1714279509</v>
+      </c>
+      <c r="E362" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F362" t="inlineStr"/>
+      <c r="G362" t="inlineStr">
+        <is>
+          <t>LivingRoom.Door001.state: open</t>
+        </is>
+      </c>
+      <c r="H362" t="inlineStr">
+        <is>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I362" t="inlineStr"/>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>Door_Operation</t>
+        </is>
+      </c>
+      <c r="C363" t="inlineStr">
+        <is>
+          <t>LivingRoom</t>
+        </is>
+      </c>
+      <c r="D363" t="n">
+        <v>1714279550</v>
+      </c>
+      <c r="E363" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F363" t="inlineStr"/>
+      <c r="G363" t="inlineStr">
+        <is>
+          <t>LivingRoom.Door001.state: close</t>
+        </is>
+      </c>
+      <c r="H363" t="inlineStr">
+        <is>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I363" t="inlineStr"/>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>Door_Operation</t>
+        </is>
+      </c>
+      <c r="C364" t="inlineStr">
+        <is>
+          <t>LivingRoom</t>
+        </is>
+      </c>
+      <c r="D364" t="n">
+        <v>1714289658</v>
+      </c>
+      <c r="E364" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F364" t="inlineStr"/>
+      <c r="G364" t="inlineStr">
+        <is>
+          <t>LivingRoom.Door001.state: open</t>
+        </is>
+      </c>
+      <c r="H364" t="inlineStr">
+        <is>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I364" t="inlineStr"/>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>Door_Operation</t>
+        </is>
+      </c>
+      <c r="C365" t="inlineStr">
+        <is>
+          <t>LivingRoom</t>
+        </is>
+      </c>
+      <c r="D365" t="n">
+        <v>1714289662</v>
+      </c>
+      <c r="E365" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F365" t="inlineStr"/>
+      <c r="G365" t="inlineStr">
+        <is>
+          <t>LivingRoom.Door001.state: close</t>
+        </is>
+      </c>
+      <c r="H365" t="inlineStr">
+        <is>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I365" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
